--- a/data/trans_camb/P16A09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Edad-trans_camb.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,41</t>
+          <t>-0,11; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,22</t>
+          <t>-0,26; 1,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,0</t>
+          <t>-1,65; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,54</t>
+          <t>-1,17; 0,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,04</t>
+          <t>-0,86; 1,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,53</t>
+          <t>-0,4; 0,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,21</t>
+          <t>-0,55; 0,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,85</t>
+          <t>-0,29; 0,9</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,95</t>
+          <t>-1,32; 0,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,42</t>
+          <t>-1,61; 0,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,29</t>
+          <t>-0,93; 1,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,55</t>
+          <t>-0,54; 0,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,44</t>
+          <t>-0,74; 0,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,97</t>
+          <t>-0,37; 0,94</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,18; 183,44</t>
+          <t>-79,07; 154,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,42; 100,69</t>
+          <t>-90,65; 123,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,43; 232,63</t>
+          <t>-57,67; 247,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,75; 241,15</t>
+          <t>-65,73; 235,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,18; 199,64</t>
+          <t>-82,42; 149,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,32; 338,39</t>
+          <t>-47,46; 361,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,65</t>
+          <t>-2,48; 0,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,12</t>
+          <t>-2,91; -0,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,98</t>
+          <t>-2,44; 0,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,81</t>
+          <t>-2,2; 1,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,25</t>
+          <t>-2,01; 2,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,23</t>
+          <t>-1,48; 3,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,74</t>
+          <t>-1,67; 0,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,62</t>
+          <t>-1,87; 0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,47</t>
+          <t>-1,63; 1,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 87,0</t>
+          <t>-87,08; 117,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,96</t>
+          <t>-100,0; 18,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,81; 86,23</t>
+          <t>-80,54; 86,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 112,53</t>
+          <t>-55,44; 118,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 139,51</t>
+          <t>-58,19; 123,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 204,64</t>
+          <t>-42,86; 159,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 48,38</t>
+          <t>-56,77; 54,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,38; 42,17</t>
+          <t>-62,19; 37,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 88,12</t>
+          <t>-53,4; 82,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -1,83</t>
+          <t>-8,07; -1,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,99; -2,79</t>
+          <t>-8,71; -2,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -2,38</t>
+          <t>-8,21; -2,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,33</t>
+          <t>-3,95; 4,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 0,28</t>
+          <t>-6,54; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 1,05</t>
+          <t>-5,36; 0,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 0,16</t>
+          <t>-4,88; 0,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; -1,92</t>
+          <t>-7,17; -2,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -1,52</t>
+          <t>-6,02; -1,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-83,68; -24,25</t>
+          <t>-82,89; -21,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,39; -38,01</t>
+          <t>-88,32; -36,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,67; -40,71</t>
+          <t>-83,06; -42,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 62,36</t>
+          <t>-35,08; 60,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 5,87</t>
+          <t>-59,97; 10,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 17,9</t>
+          <t>-46,54; 15,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 3,12</t>
+          <t>-50,67; 4,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-68,28; -27,55</t>
+          <t>-70,74; -30,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,7; -21,09</t>
+          <t>-59,73; -23,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 2,37</t>
+          <t>-4,59; 2,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,71; -0,19</t>
+          <t>-6,36; -0,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,08</t>
+          <t>-6,37; -0,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 5,4</t>
+          <t>-5,11; 5,71</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,15; -1,81</t>
+          <t>-10,89; -1,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -1,15</t>
+          <t>-15,52; -0,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,62</t>
+          <t>-4,18; 2,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,73; -1,64</t>
+          <t>-8,24; -1,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,73; -1,78</t>
+          <t>-9,03; -1,83</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 79,97</t>
+          <t>-60,21; 70,3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-78,26; 6,11</t>
+          <t>-78,96; 6,12</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 1,59</t>
+          <t>-73,41; -2,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 43,67</t>
+          <t>-29,1; 41,84</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,56; -14,09</t>
+          <t>-60,89; -13,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,62; -7,91</t>
+          <t>-78,83; -6,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 28,76</t>
+          <t>-32,17; 29,81</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -15,43</t>
+          <t>-60,93; -18,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-71,37; -17,51</t>
+          <t>-68,92; -19,74</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 2,77</t>
+          <t>-10,75; 2,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-16,46; -4,83</t>
+          <t>-17,2; -4,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,13; -5,87</t>
+          <t>-18,02; -6,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 10,99</t>
+          <t>-1,37; 10,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 0,08</t>
+          <t>-10,92; 0,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 0,89</t>
+          <t>-8,53; 1,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 6,27</t>
+          <t>-3,29; 5,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,73; -3,2</t>
+          <t>-11,4; -3,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,35; -2,88</t>
+          <t>-11,15; -3,26</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 21,16</t>
+          <t>-51,03; 19,31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-73,47; -30,34</t>
+          <t>-75,03; -28,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-76,49; -41,47</t>
+          <t>-77,0; -40,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 78,66</t>
+          <t>-7,06; 74,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,78; 2,69</t>
+          <t>-53,64; 0,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 6,42</t>
+          <t>-39,91; 8,17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 41,42</t>
+          <t>-16,82; 34,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-56,91; -18,91</t>
+          <t>-57,42; -21,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-50,44; -19,55</t>
+          <t>-51,4; -21,02</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,71; -0,03</t>
+          <t>-1,57; -0,11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,88</t>
+          <t>-2,28; -0,92</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,95; -0,39</t>
+          <t>-1,91; -0,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,89</t>
+          <t>-0,29; 1,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,32</t>
+          <t>-2,3; -0,3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,02</t>
+          <t>-1,17; 1,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,67</t>
+          <t>-0,75; 0,64</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; -0,79</t>
+          <t>-2,07; -0,76</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,1</t>
+          <t>-1,22; 0,17</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,99; -0,8</t>
+          <t>-47,73; -3,3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,52; -34,48</t>
+          <t>-69,12; -35,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-56,79; -15,98</t>
+          <t>-57,57; -16,46</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 42,16</t>
+          <t>-5,0; 44,72</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -6,12</t>
+          <t>-41,15; -6,34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 22,36</t>
+          <t>-20,76; 26,18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 18,43</t>
+          <t>-17,57; 17,09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-46,32; -21,57</t>
+          <t>-47,11; -20,6</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 2,89</t>
+          <t>-28,53; 4,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,66</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,4</t>
+          <t>-0,11; 1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,22</t>
+          <t>-0,26; 1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,54</t>
+          <t>-1,17; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,08</t>
+          <t>-0,76; 1,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,52</t>
+          <t>-0,41; 0,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,25</t>
+          <t>-0,54; 0,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,9</t>
+          <t>-0,35; 0,84</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132,35%</t>
+          <t>122,02%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,3</t>
         </is>
       </c>
     </row>
@@ -1109,37 +1109,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,87</t>
+          <t>-1,26; 0,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,41</t>
+          <t>-1,66; 0,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,33</t>
+          <t>-0,97; 1,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,55</t>
+          <t>-0,61; 0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,94</t>
+          <t>-0,32; 0,9</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 154,88</t>
+          <t>-74,57; 224,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,65; 123,54</t>
+          <t>-90,53; 109,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,67; 247,93</t>
+          <t>-61,03; 232,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,73; 235,67</t>
+          <t>-72,64; 179,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,42; 149,99</t>
+          <t>-80,76; 151,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 361,01</t>
+          <t>-41,25; 303,55</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,71</t>
+          <t>-2,39; 0,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,12</t>
+          <t>-2,95; -0,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,99</t>
+          <t>-1,62; 1,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,79</t>
+          <t>-2,03; 1,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,0</t>
+          <t>-1,99; 2,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,01</t>
+          <t>-1,8; 1,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,83</t>
+          <t>-1,68; 0,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,56</t>
+          <t>-1,79; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,41</t>
+          <t>-1,19; 1,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-24,07%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,13%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,08; 117,85</t>
+          <t>-86,55; 83,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,64</t>
+          <t>-100,0; 13,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,54; 86,79</t>
+          <t>-60,7; 140,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 118,91</t>
+          <t>-53,22; 118,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,19; 123,88</t>
+          <t>-51,73; 136,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 159,8</t>
+          <t>-45,62; 123,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,77; 54,95</t>
+          <t>-56,15; 51,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,19; 37,29</t>
+          <t>-60,86; 34,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 82,69</t>
+          <t>-38,84; 78,32</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-3,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -1,44</t>
+          <t>-8,23; -1,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -2,33</t>
+          <t>-8,48; -2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,21; -2,36</t>
+          <t>-8,17; -2,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,01</t>
+          <t>-3,81; 4,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 0,32</t>
+          <t>-7,03; -0,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,94</t>
+          <t>-5,84; 0,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,28</t>
+          <t>-4,94; 0,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -2,2</t>
+          <t>-6,82; -2,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -1,68</t>
+          <t>-5,88; -1,53</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-68,08%</t>
+          <t>-68,12%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-23,08%</t>
+          <t>-23,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-44,13%</t>
+          <t>-43,84%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-82,89; -21,04</t>
+          <t>-83,93; -27,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,32; -36,07</t>
+          <t>-87,13; -32,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,06; -42,25</t>
+          <t>-83,08; -38,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 60,76</t>
+          <t>-34,62; 62,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 10,48</t>
+          <t>-63,46; 0,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,54; 15,8</t>
+          <t>-49,32; 12,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 4,88</t>
+          <t>-50,8; 2,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-70,74; -30,24</t>
+          <t>-68,86; -29,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,73; -23,95</t>
+          <t>-59,04; -22,21</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-2,83</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-6,98</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-2,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,68</t>
+          <t>-5,09; 2,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -0,06</t>
+          <t>-6,48; 0,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -0,29</t>
+          <t>-6,2; -0,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 5,71</t>
+          <t>-5,5; 5,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -1,91</t>
+          <t>-11,44; -1,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,52; -0,97</t>
+          <t>-6,26; 2,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,97</t>
+          <t>-4,33; 2,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -1,94</t>
+          <t>-7,96; -1,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,03; -1,83</t>
+          <t>-5,82; 0,11</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-47,33%</t>
+          <t>-47,27%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-45,04%</t>
+          <t>-14,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-41,57%</t>
+          <t>-24,45%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 70,3</t>
+          <t>-63,53; 62,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 6,12</t>
+          <t>-79,01; 9,16</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,41; -2,19</t>
+          <t>-73,96; 1,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 41,84</t>
+          <t>-29,1; 44,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,89; -13,48</t>
+          <t>-61,79; -12,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,83; -6,15</t>
+          <t>-34,77; 16,49</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 29,81</t>
+          <t>-33,91; 26,23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,93; -18,85</t>
+          <t>-60,89; -20,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,92; -19,74</t>
+          <t>-42,75; 2,72</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-11,26</t>
+          <t>-11,2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-6,49</t>
+          <t>-6,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 2,96</t>
+          <t>-10,97; 2,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-17,2; -4,57</t>
+          <t>-16,87; -4,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-18,02; -6,3</t>
+          <t>-17,1; -6,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,75</t>
+          <t>-1,09; 11,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 0,01</t>
+          <t>-10,93; -0,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 1,04</t>
+          <t>-8,23; 1,77</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,41</t>
+          <t>-3,12; 5,83</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -3,4</t>
+          <t>-11,46; -3,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,15; -3,26</t>
+          <t>-10,07; -2,34</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-62,51%</t>
+          <t>-62,16%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-19,15%</t>
+          <t>-17,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-36,81%</t>
+          <t>-35,73%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,03; 19,31</t>
+          <t>-51,53; 20,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-75,03; -28,46</t>
+          <t>-74,93; -31,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-77,0; -40,72</t>
+          <t>-77,64; -42,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 74,43</t>
+          <t>-6,09; 79,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 0,83</t>
+          <t>-53,38; -0,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 8,17</t>
+          <t>-38,88; 13,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 34,45</t>
+          <t>-15,42; 38,31</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-57,42; -21,79</t>
+          <t>-57,08; -20,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-51,4; -21,02</t>
+          <t>-50,12; -16,66</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,11</t>
+          <t>-1,59; 0,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,92</t>
+          <t>-2,31; -0,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,91; -0,43</t>
+          <t>-1,82; -0,34</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,9</t>
+          <t>-0,34; 1,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,3</t>
+          <t>-2,29; -0,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,2</t>
+          <t>-0,55; 1,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,64</t>
+          <t>-0,72; 0,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,07; -0,76</t>
+          <t>-2,02; -0,84</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,17</t>
+          <t>-0,95; 0,28</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-39,75%</t>
+          <t>-35,94%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-13,43%</t>
+          <t>-7,43%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,73; -3,3</t>
+          <t>-47,8; 1,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,12; -35,13</t>
+          <t>-68,14; -33,94</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-57,57; -16,46</t>
+          <t>-54,17; -12,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 44,72</t>
+          <t>-6,1; 42,58</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-41,15; -6,34</t>
+          <t>-41,89; -6,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 26,18</t>
+          <t>-9,38; 30,58</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 17,09</t>
+          <t>-16,41; 16,59</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-47,11; -20,6</t>
+          <t>-46,62; -22,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 4,57</t>
+          <t>-21,57; 8,15</t>
         </is>
       </c>
     </row>
